--- a/ArchivosExcel/Lugares_DireccionesRevisadas.xlsx
+++ b/ArchivosExcel/Lugares_DireccionesRevisadas.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Av. Cuauhtémoc 330, Doctores, Cuauhtémoc, 06720 Ciudad de México, CDMX</t>
+          <t>Av. Cuauhtémoc 330, Doctores, Cuauhtémoc, 06720 Ciudad de México, CDMX, México</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tlacotalpan 59, Centro Urbano Pdte. Juárez, Roma Sur, Cuauhtémoc, 06760 Cuauhtémoc, CDMX</t>
+          <t>Tlacotalpan 59, Centro Urbano Pdte. Juárez, Roma Sur, Cuauhtémoc, 06760 Cuauhtémoc, CDMX, México</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blvd. Milenio 130, San Carlos la Roncha, 37544 León de los Aldama, Gto.</t>
+          <t>Blvd. Milenio 130, San Carlos la Roncha, 37544 León de los Aldama, Gto., México</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
